--- a/Tools.Config/GameConfig/Datas/shop_goods.xlsx
+++ b/Tools.Config/GameConfig/Datas/shop_goods.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,35 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -68,15 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -442,120 +413,128 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>goodsId</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>goodsGroupId</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>itemId</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>itemName</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>buyLimit</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>rewardItemCount</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>unlockRule</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>effectDesc</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -569,52 +548,62 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>商品ID</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>商品组ID；关联 shop.goodsGroupId</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>物品ID；后续关联 item/weapon 表</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>奖励道具ID</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>商品显示名</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>价格</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>货币类型，例如 Gold</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>货币类型：Gold/Diamond/EventToken</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>购买上限，0表示不限</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>每次购买获得数量</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>解锁条件，空表示默认解锁</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>中文说明</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>效果说明</t>
         </is>
@@ -622,69 +611,83 @@
     </row>
     <row r="5">
       <c r="B5" t="n">
-        <v>100101</v>
+        <v>200101</v>
       </c>
       <c r="C5" t="n">
+        <v>2001</v>
+      </c>
+      <c r="D5" t="n">
         <v>1001</v>
       </c>
-      <c r="D5" t="n">
-        <v>2001</v>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>粗制战斧</t>
+          <t>普通抽奖券</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>巨魔武器商店默认商品。</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>购买后提高巨魔近战攻击能力。</t>
+      <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>常驻补给</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>获得 1 张普通抽奖券</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
-        <v>100102</v>
+        <v>300101</v>
       </c>
       <c r="C6" t="n">
-        <v>1001</v>
+        <v>3001</v>
       </c>
       <c r="D6" t="n">
-        <v>2002</v>
+        <v>1301</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>骨质护甲</t>
+          <t>活动兑换碎片</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>巨魔武器商店默认商品。</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>购买后提高巨魔生存能力。</t>
+          <t>EventToken</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>99</v>
+      </c>
+      <c r="I6" t="n">
+        <v>10</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>开服活动商品</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>获得 10 个活动兑换碎片</t>
         </is>
       </c>
     </row>
